--- a/files/13-1524-granville-ave.xlsx
+++ b/files/13-1524-granville-ave.xlsx
@@ -8,17 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iniculete\LAAA-Deploys\onmarket\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{97CF9E7D-AAE2-4009-819F-CA1194643991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C0CBADBD-7BC1-463E-9D02-ACC08BECF3A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{58E7793E-940E-48F2-984C-63AFBCEC6B24}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{46DF4A20-4A87-4C08-BC09-1A51246A3808}"/>
   </bookViews>
   <sheets>
     <sheet name="Assumptions" sheetId="1" r:id="rId1"/>
     <sheet name="13 1524 Granville Ave" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'13 1524 Granville Ave'!$A$1:$N$78</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -43,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="142">
   <si>
     <t>LAAA UNDERWRITING BENCHMARKS (edit here; every deal tab reads these)</t>
   </si>
@@ -195,10 +192,10 @@
     <t>LoopNet listing</t>
   </si>
   <si>
-    <t>Data pulled 9/17/2026 from LoopNet public listing</t>
-  </si>
-  <si>
-    <t>NOTE: 1988 build, RSO exempt</t>
+    <t>Data pulled 9/17/2026 from LoopNet public listing + rent roll and expenses read from the listing broker's OM (Lyon Stahl / Serhant / Taksa, rent roll 9/1/2026)</t>
+  </si>
+  <si>
+    <t>NOTE: 1988 build, RSO exempt | OM: Rent roll is labeled 'Rent (Effective 9/1/26)', i.e. forward-dated to Sept 1, 2026, not a historical in-place roll.; PH3 (3+3) is vacant as of 9/1/26 and is carried in scheduled rent at the $4,850 market asking rent; without it in-place monthly rent is $31,995.; Unit 102 shows a 7/29/26 move-in at $ | OM: Rent roll is labeled 'Rent (Effective 9/1/26)', i.e. forward-dated to Sept 1, 2026, not a historical in-place roll.; PH3 (3+3) is vacant as of 9/1/26 and is carried in scheduled rent at the $4,850 market asking rent; without it in-place monthly rent is $31,995.; Unit 102 shows a 7/29/26 move-in at $</t>
   </si>
   <si>
     <t>PROPERTY</t>
@@ -303,13 +300,13 @@
     <t>Rent source</t>
   </si>
   <si>
-    <t>2 Bd / 2.5 Ba  (~1200 SF)</t>
-  </si>
-  <si>
-    <t>Allocated from published GRM (price / GRM) using LAAA bed weights</t>
-  </si>
-  <si>
-    <t>3 Bd / 3 Ba  (~1300 SF)</t>
+    <t>2 Bd / 2.5 Ba  [Units 101-107, townhouse-style; rents $2,910-$3,700; monthly]</t>
+  </si>
+  <si>
+    <t>OM rent roll, current in-place rents (OM rent roll 9/1/2026)</t>
+  </si>
+  <si>
+    <t>3 Bd / 3 Ba  [PH1-PH3 penthouses with private rooftop decks; PH1 $3,750, P]</t>
   </si>
   <si>
     <t>Total / weighted avg</t>
@@ -330,7 +327,7 @@
     <t>Scheduled gross rent</t>
   </si>
   <si>
-    <t>OM column: price / published GRM</t>
+    <t>OM column: OM stated current scheduled rent (OM rent roll 9/1/2026); LAAA column: OM rent roll by unit type</t>
   </si>
   <si>
     <t>Other income (laundry, parking, RUBS)</t>
@@ -342,7 +339,7 @@
     <t>Vacancy &amp; credit loss</t>
   </si>
   <si>
-    <t>OM 3.0% (OM figure if extracted, else 3% assumed); LAAA per Assumptions</t>
+    <t>OM 3.0%; LAAA per Assumptions</t>
   </si>
   <si>
     <t>Effective gross income</t>
@@ -387,7 +384,7 @@
     <t>Utilities (water/sewer/trash/common electric &amp; gas)</t>
   </si>
   <si>
-    <t>per unit, by city</t>
+    <t>per unit, by city; OM utilities + water/sewer + gas/electric + trash combined</t>
   </si>
   <si>
     <t>Contract services (landscape, pest, cleaning)</t>
@@ -396,10 +393,10 @@
     <t>per unit</t>
   </si>
   <si>
-    <t>Admin / legal / licenses / rent registration</t>
-  </si>
-  <si>
-    <t>per unit; OM "other" items land here</t>
+    <t>Admin / legal / licenses / rent registration / other OM items</t>
+  </si>
+  <si>
+    <t>OM other items: Direct Assessments (2026 annualized) 3,357; Maintenance Supplies (2026 annualized) 3,130; Utilities - Telephone (2026 annualized) 1,461; Elevator (2026 annualized) 2,229; Services (202</t>
   </si>
   <si>
     <t>Replacement reserves</t>
@@ -408,7 +405,7 @@
     <t>Total operating expenses</t>
   </si>
   <si>
-    <t>OM line items not published. OM total IMPLIED = OM EGI - (price x published cap)</t>
+    <t>OM line items from OM (OM rent roll 9/1/2026); basis: OM 'Current' column of the Pro Forma Annual Operating Expenses page. Mixed basis: taxes projected at 1.187% x $5,250,000 list price (not seller actual), management projected at 4.0% of GOI, reserves projected at $200/unit; insurance is 2026 actual ($0.51/GSF); R&amp;M is $1,200/unit annualized; all remaining lines are 2026 annualized actuals. Gas and electric are separately metered (tenant-paid), so no owner gas/electric line. Total 31.22% of SGI. Market column is $140,062 (only management changes).; OM total 138,058</t>
   </si>
   <si>
     <t>Expenses per unit</t>
@@ -424,6 +421,9 @@
   </si>
   <si>
     <t>Net operating income</t>
+  </si>
+  <si>
+    <t>OM states NOI 290,818 / cap 5.54</t>
   </si>
   <si>
     <t>Cap rate on asking price</t>
@@ -472,12 +472,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="\$#,##0;\(\$#,##0\);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="166" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0;\(&quot;$&quot;#,##0\);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -525,6 +526,7 @@
       <sz val="11"/>
       <color rgb="FFC00000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -533,8 +535,21 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF595959"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -562,7 +577,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF9E5"/>
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -598,7 +614,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -622,12 +638,15 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -660,7 +679,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C47652B1-78F2-4652-93FE-837D7633C9BB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{66B6384B-13E8-43C2-855E-48D2E38CA3B3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -971,7 +990,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70B2613A-D095-4850-B679-9AE0139335FD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE96C07C-DB75-41D4-9B4D-FE374D6ABCBF}">
   <dimension ref="A1:C40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1340,7 +1359,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F234B012-FA5B-4EC5-8F77-84CA61E45765}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AEF4520-0309-471B-B019-7C7126792F27}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1574,17 +1593,17 @@
         <v>7</v>
       </c>
       <c r="C30" s="21">
-        <v>3385</v>
-      </c>
-      <c r="D30" s="8">
+        <v>3435</v>
+      </c>
+      <c r="D30" s="22">
         <f>B30*C30</f>
-        <v>23695</v>
-      </c>
-      <c r="E30" s="8">
+        <v>24045</v>
+      </c>
+      <c r="E30" s="22">
         <f>D30*12</f>
-        <v>284340</v>
-      </c>
-      <c r="F30" s="2" t="s">
+        <v>288540</v>
+      </c>
+      <c r="F30" s="23" t="s">
         <v>87</v>
       </c>
     </row>
@@ -1596,39 +1615,39 @@
         <v>3</v>
       </c>
       <c r="C31" s="21">
-        <v>4388</v>
-      </c>
-      <c r="D31" s="8">
+        <v>4267</v>
+      </c>
+      <c r="D31" s="22">
         <f>B31*C31</f>
-        <v>13164</v>
-      </c>
-      <c r="E31" s="8">
+        <v>12801</v>
+      </c>
+      <c r="E31" s="22">
         <f>D31*12</f>
-        <v>157968</v>
-      </c>
-      <c r="F31" s="2" t="s">
+        <v>153612</v>
+      </c>
+      <c r="F31" s="23" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="22" t="s">
+      <c r="A32" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="B32" s="23">
+      <c r="B32" s="25">
         <f>SUM(B30:B31)</f>
         <v>10</v>
       </c>
-      <c r="C32" s="24">
+      <c r="C32" s="26">
         <f>IFERROR(D32/B32,"")</f>
-        <v>3685.9</v>
-      </c>
-      <c r="D32" s="24">
+        <v>3684.6</v>
+      </c>
+      <c r="D32" s="26">
         <f>SUM(D30:D31)</f>
-        <v>36859</v>
-      </c>
-      <c r="E32" s="24">
+        <v>36846</v>
+      </c>
+      <c r="E32" s="26">
         <f>SUM(E30:E31)</f>
-        <v>442308</v>
+        <v>442152</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1642,16 +1661,16 @@
       <c r="F34" s="14"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="25"/>
-      <c r="B35" s="25" t="s">
+      <c r="A35" s="27"/>
+      <c r="B35" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="C35" s="25" t="s">
+      <c r="C35" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="D35" s="25"/>
-      <c r="E35" s="25"/>
-      <c r="F35" s="25" t="s">
+      <c r="D35" s="27"/>
+      <c r="E35" s="27"/>
+      <c r="F35" s="27" t="s">
         <v>93</v>
       </c>
     </row>
@@ -1659,12 +1678,12 @@
       <c r="A36" t="s">
         <v>94</v>
       </c>
-      <c r="B36" s="8">
-        <v>442291.49115417019</v>
+      <c r="B36" s="22">
+        <v>442140</v>
       </c>
       <c r="C36" s="8">
         <f>E32</f>
-        <v>442308</v>
+        <v>442152</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>95</v>
@@ -1682,16 +1701,16 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="22" t="s">
+      <c r="A38" s="24" t="s">
         <v>97</v>
       </c>
       <c r="B38" s="8">
         <f>B36+B37</f>
-        <v>442291.49115417019</v>
+        <v>442140</v>
       </c>
       <c r="C38" s="8">
         <f>C36+C37</f>
-        <v>442308</v>
+        <v>442152</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1700,27 +1719,27 @@
       </c>
       <c r="B39" s="8">
         <f>-B36*0.03</f>
-        <v>-13268.744734625105</v>
+        <v>-13264.199999999999</v>
       </c>
       <c r="C39" s="8">
         <f>-C36*Assumptions!$B$3</f>
-        <v>-13269.24</v>
+        <v>-13264.56</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="22" t="s">
+      <c r="A40" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="B40" s="24">
+      <c r="B40" s="26">
         <f>B38+B39</f>
-        <v>429022.74641954509</v>
-      </c>
-      <c r="C40" s="24">
+        <v>428875.8</v>
+      </c>
+      <c r="C40" s="26">
         <f>C38+C39</f>
-        <v>429038.76</v>
+        <v>428887.44</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -1734,22 +1753,22 @@
       <c r="F42" s="14"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="25" t="s">
+      <c r="A43" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="B43" s="25" t="s">
+      <c r="B43" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="C43" s="25" t="s">
+      <c r="C43" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="D43" s="25" t="s">
+      <c r="D43" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="E43" s="25" t="s">
+      <c r="E43" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="F43" s="25" t="s">
+      <c r="F43" s="27" t="s">
         <v>93</v>
       </c>
     </row>
@@ -1757,18 +1776,20 @@
       <c r="A44" t="s">
         <v>105</v>
       </c>
-      <c r="B44" s="8"/>
+      <c r="B44" s="22">
+        <v>62337</v>
+      </c>
       <c r="C44" s="8">
         <f>B22*Assumptions!$B$15</f>
         <v>65625</v>
       </c>
-      <c r="D44" s="26">
+      <c r="D44" s="28">
         <f>C44</f>
         <v>65625</v>
       </c>
-      <c r="E44" s="8" t="str">
+      <c r="E44" s="8">
         <f t="shared" ref="E44:E52" si="0">IF(ISNUMBER(B44),D44-B44,"")</f>
-        <v/>
+        <v>3288</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>106</v>
@@ -1778,18 +1799,20 @@
       <c r="A45" t="s">
         <v>107</v>
       </c>
-      <c r="B45" s="8"/>
+      <c r="B45" s="22">
+        <v>7315</v>
+      </c>
       <c r="C45" s="8">
         <f>B7*Assumptions!$B$5+B8*Assumptions!$B$6</f>
         <v>16298</v>
       </c>
-      <c r="D45" s="26">
+      <c r="D45" s="28">
         <f t="shared" ref="D45:D51" si="1">IF(ISNUMBER(B45),MAX(B45,C45),C45)</f>
         <v>16298</v>
       </c>
-      <c r="E45" s="8" t="str">
+      <c r="E45" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>8983</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>108</v>
@@ -1799,18 +1822,20 @@
       <c r="A46" t="s">
         <v>109</v>
       </c>
-      <c r="B46" s="8"/>
+      <c r="B46" s="22">
+        <v>17155</v>
+      </c>
       <c r="C46" s="8">
         <f>C40*Assumptions!$B$4</f>
-        <v>21451.938000000002</v>
-      </c>
-      <c r="D46" s="26">
+        <v>21444.372000000003</v>
+      </c>
+      <c r="D46" s="28">
         <f t="shared" si="1"/>
-        <v>21451.938000000002</v>
-      </c>
-      <c r="E46" s="8" t="str">
+        <v>21444.372000000003</v>
+      </c>
+      <c r="E46" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>4289.372000000003</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>110</v>
@@ -1820,18 +1845,20 @@
       <c r="A47" t="s">
         <v>111</v>
       </c>
-      <c r="B47" s="8"/>
+      <c r="B47" s="22">
+        <v>12000</v>
+      </c>
       <c r="C47" s="8">
         <f>B7*Assumptions!$B$7</f>
         <v>12000</v>
       </c>
-      <c r="D47" s="26">
+      <c r="D47" s="28">
         <f t="shared" si="1"/>
         <v>12000</v>
       </c>
-      <c r="E47" s="8" t="str">
+      <c r="E47" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>112</v>
@@ -1841,18 +1868,20 @@
       <c r="A48" t="s">
         <v>113</v>
       </c>
-      <c r="B48" s="8"/>
+      <c r="B48" s="22">
+        <v>22652</v>
+      </c>
       <c r="C48" s="8">
         <f>B7*Assumptions!$B$9</f>
         <v>15000</v>
       </c>
-      <c r="D48" s="26">
+      <c r="D48" s="28">
         <f t="shared" si="1"/>
-        <v>15000</v>
-      </c>
-      <c r="E48" s="8" t="str">
+        <v>22652</v>
+      </c>
+      <c r="E48" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>114</v>
@@ -1862,18 +1891,20 @@
       <c r="A49" t="s">
         <v>115</v>
       </c>
-      <c r="B49" s="8"/>
+      <c r="B49" s="22">
+        <v>4156</v>
+      </c>
       <c r="C49" s="8">
         <f>B7*Assumptions!$B$12</f>
         <v>4000</v>
       </c>
-      <c r="D49" s="26">
+      <c r="D49" s="28">
         <f t="shared" si="1"/>
-        <v>4000</v>
-      </c>
-      <c r="E49" s="8" t="str">
+        <v>4156</v>
+      </c>
+      <c r="E49" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>116</v>
@@ -1883,18 +1914,20 @@
       <c r="A50" t="s">
         <v>117</v>
       </c>
-      <c r="B50" s="8"/>
+      <c r="B50" s="22">
+        <v>10443</v>
+      </c>
       <c r="C50" s="8">
         <f>B7*Assumptions!$B$13</f>
         <v>2500</v>
       </c>
-      <c r="D50" s="26">
+      <c r="D50" s="28">
         <f t="shared" si="1"/>
-        <v>2500</v>
-      </c>
-      <c r="E50" s="8" t="str">
+        <v>10443</v>
+      </c>
+      <c r="E50" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>118</v>
@@ -1904,42 +1937,44 @@
       <c r="A51" t="s">
         <v>119</v>
       </c>
-      <c r="B51" s="8"/>
+      <c r="B51" s="22">
+        <v>2000</v>
+      </c>
       <c r="C51" s="8">
         <f>B7*Assumptions!$B$14</f>
         <v>3000</v>
       </c>
-      <c r="D51" s="26">
+      <c r="D51" s="28">
         <f t="shared" si="1"/>
         <v>3000</v>
       </c>
-      <c r="E51" s="8" t="str">
+      <c r="E51" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="22" t="s">
+      <c r="A52" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="B52" s="24">
-        <f>B40-B22*B25</f>
-        <v>138172.74641954509</v>
-      </c>
-      <c r="C52" s="24">
+      <c r="B52" s="26">
+        <f>SUM(B44:B51)</f>
+        <v>138058</v>
+      </c>
+      <c r="C52" s="26">
         <f>SUM(C44:C51)</f>
-        <v>139874.93799999999</v>
-      </c>
-      <c r="D52" s="24">
+        <v>139867.372</v>
+      </c>
+      <c r="D52" s="26">
         <f>SUM(D44:D51)</f>
-        <v>139874.93799999999</v>
-      </c>
-      <c r="E52" s="24">
+        <v>155618.372</v>
+      </c>
+      <c r="E52" s="26">
         <f t="shared" si="0"/>
-        <v>1702.1915804549062</v>
+        <v>17560.372000000003</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>121</v>
@@ -1951,15 +1986,15 @@
       </c>
       <c r="B53" s="8">
         <f>IFERROR(B52/B7,"")</f>
-        <v>13817.274641954509</v>
+        <v>13805.8</v>
       </c>
       <c r="C53" s="8">
         <f>IFERROR(C52/B7,"")</f>
-        <v>13987.4938</v>
+        <v>13986.7372</v>
       </c>
       <c r="D53" s="8">
         <f>IFERROR(D52/B7,"")</f>
-        <v>13987.4938</v>
+        <v>15561.8372</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -1968,24 +2003,24 @@
       </c>
       <c r="B54" s="18">
         <f>IFERROR(B52/B40,"")</f>
-        <v>0.32206391752577324</v>
+        <v>0.32190671518420949</v>
       </c>
       <c r="C54" s="18">
         <f>IFERROR(C52/C40,"")</f>
-        <v>0.3260193507924552</v>
+        <v>0.32611673589695234</v>
       </c>
       <c r="D54" s="18">
         <f>IF(C36&gt;0,IFERROR(D52/C40,""),"")</f>
-        <v>0.3260193507924552</v>
+        <v>0.36284198949729096</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="22" t="s">
+      <c r="A55" s="24" t="s">
         <v>124</v>
       </c>
-      <c r="B55" s="12" t="str">
+      <c r="B55" s="29" t="str">
         <f>IF(ISNUMBER(B52),IF(D52&gt;B52*(1+Assumptions!$B$24),"OM EXPENSES LIGHT","OM expenses reasonable"),"OM expenses not published")</f>
-        <v>OM expenses reasonable</v>
+        <v>OM EXPENSES LIGHT</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -1999,77 +2034,80 @@
       <c r="F57" s="14"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="25"/>
-      <c r="B58" s="25" t="s">
+      <c r="A58" s="27"/>
+      <c r="B58" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="C58" s="25" t="s">
+      <c r="C58" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="D58" s="25"/>
-      <c r="E58" s="25"/>
-      <c r="F58" s="25" t="s">
+      <c r="D58" s="27"/>
+      <c r="E58" s="27"/>
+      <c r="F58" s="27" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="22" t="s">
+      <c r="A59" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="B59" s="24">
+      <c r="B59" s="26">
         <f>B40-B52</f>
-        <v>290850</v>
-      </c>
-      <c r="C59" s="24">
+        <v>290817.8</v>
+      </c>
+      <c r="C59" s="26">
         <f>IF(C36&gt;0,C40-D52,"")</f>
-        <v>289163.82200000004</v>
+        <v>273269.06799999997</v>
+      </c>
+      <c r="F59" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="22" t="s">
-        <v>127</v>
+      <c r="A60" s="24" t="s">
+        <v>128</v>
       </c>
       <c r="B60" s="18">
         <f>IFERROR(B59/B22,"")</f>
-        <v>5.5399999999999998E-2</v>
+        <v>5.5393866666666666E-2</v>
       </c>
       <c r="C60" s="18">
         <f>IF(C59="","",IFERROR(C59/B22,""))</f>
-        <v>5.5078823238095244E-2</v>
+        <v>5.205125104761904E-2</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B61" s="19">
         <f>IFERROR(B22/B36,"")</f>
-        <v>11.87</v>
+        <v>11.874067037589903</v>
       </c>
       <c r="C61" s="19">
         <f>IF(C36&gt;0,IFERROR(B22/C36,""),"")</f>
-        <v>11.869556960308202</v>
+        <v>11.873744775552298</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B62" s="8">
         <f>IFERROR(B59/B7,"")</f>
-        <v>29085</v>
+        <v>29081.78</v>
       </c>
       <c r="C62" s="8">
         <f>IF(C59="","",IFERROR(C59/B7,""))</f>
-        <v>28916.382200000004</v>
+        <v>27326.906799999997</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B64" s="14"/>
       <c r="C64" s="14"/>
@@ -2079,7 +2117,7 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B65" s="8">
         <f>IFERROR(B22*Assumptions!$B$20,"")</f>
@@ -2088,79 +2126,78 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B66" s="8">
         <f>IF(C59="","",IFERROR(PV(Assumptions!$B$22/12,Assumptions!$B$23*12,-C59/Assumptions!$B$21/12),""))</f>
-        <v>3130915.9659634833</v>
+        <v>2958815.8092790758</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="22" t="s">
-        <v>134</v>
+      <c r="A67" s="24" t="s">
+        <v>135</v>
       </c>
       <c r="B67" s="8">
         <f>IFERROR(MIN(B65,B66),"")</f>
-        <v>3130915.9659634833</v>
+        <v>2958815.8092790758</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B68" s="8">
         <f>IFERROR(B22-B67,"")</f>
-        <v>2119084.0340365167</v>
+        <v>2291184.1907209242</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B69" s="8">
         <f>IFERROR(-PMT(Assumptions!$B$22/12,Assumptions!$B$23*12,B67)*12,"")</f>
-        <v>231331.05759999927</v>
+        <v>218615.25439999931</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B70" s="19">
         <f>IFERROR(C59/B69,"")</f>
-        <v>1.2500000000000042</v>
+        <v>1.2500000000000038</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B71" s="8">
         <f>IFERROR(C59-B69,"")</f>
-        <v>57832.764400000771</v>
+        <v>54653.813600000663</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B72" s="18">
         <f>IFERROR(B71/B68,"")</f>
-        <v>2.7291397354279805E-2</v>
+        <v>2.3853958935882744E-2</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A3" r:id="rId1" xr:uid="{974B10AE-8560-4ACD-9992-FBDDC92F9B09}"/>
+    <hyperlink ref="A3" r:id="rId1" xr:uid="{FA66F9DF-AF63-4DD7-800C-9117B17C3F8C}"/>
   </hyperlinks>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.5" footer="0.5"/>
-  <pageSetup scale="50" orientation="landscape" r:id="rId2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" r:id="rId2"/>
   <drawing r:id="rId3"/>
 </worksheet>
 </file>
--- a/files/13-1524-granville-ave.xlsx
+++ b/files/13-1524-granville-ave.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iniculete\LAAA-Deploys\onmarket\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C0CBADBD-7BC1-463E-9D02-ACC08BECF3A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6AFBC98A-8441-4821-AE18-1090E4E051BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{46DF4A20-4A87-4C08-BC09-1A51246A3808}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{426DCE90-CE74-45C0-AC7C-2C198EDE3732}"/>
   </bookViews>
   <sheets>
     <sheet name="Assumptions" sheetId="1" r:id="rId1"/>
@@ -195,7 +195,7 @@
     <t>Data pulled 9/17/2026 from LoopNet public listing + rent roll and expenses read from the listing broker's OM (Lyon Stahl / Serhant / Taksa, rent roll 9/1/2026)</t>
   </si>
   <si>
-    <t>NOTE: 1988 build, RSO exempt | OM: Rent roll is labeled 'Rent (Effective 9/1/26)', i.e. forward-dated to Sept 1, 2026, not a historical in-place roll.; PH3 (3+3) is vacant as of 9/1/26 and is carried in scheduled rent at the $4,850 market asking rent; without it in-place monthly rent is $31,995.; Unit 102 shows a 7/29/26 move-in at $ | OM: Rent roll is labeled 'Rent (Effective 9/1/26)', i.e. forward-dated to Sept 1, 2026, not a historical in-place roll.; PH3 (3+3) is vacant as of 9/1/26 and is carried in scheduled rent at the $4,850 market asking rent; without it in-place monthly rent is $31,995.; Unit 102 shows a 7/29/26 move-in at $</t>
+    <t>NOTE: 1988 build, RSO exempt | OM: Rent roll is labeled 'Rent (Effective 9/1/26)', i.e. forward-dated to Sept 1, 2026, not a historical in-place roll.; PH3 (3+3) is vacant as of 9/1/26 and is carried in scheduled rent at the $4,850 market asking rent; without it in-place monthly rent is $31,995.; Unit 102 shows a 7/29/26 move-in at $</t>
   </si>
   <si>
     <t>PROPERTY</t>
@@ -679,7 +679,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{66B6384B-13E8-43C2-855E-48D2E38CA3B3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E3DF0979-3F60-45F5-AB8A-16FCDF6E11FB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -990,7 +990,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE96C07C-DB75-41D4-9B4D-FE374D6ABCBF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32154B25-9113-4407-830F-6CC8C8F52A4E}">
   <dimension ref="A1:C40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1359,7 +1359,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AEF4520-0309-471B-B019-7C7126792F27}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97EC1E8E-B735-41BA-9E84-57229D16F3F0}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2194,7 +2194,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A3" r:id="rId1" xr:uid="{FA66F9DF-AF63-4DD7-800C-9117B17C3F8C}"/>
+    <hyperlink ref="A3" r:id="rId1" xr:uid="{A3884033-1B7E-444C-91AF-D1EA0109201B}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" r:id="rId2"/>
